--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127720671</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127720568</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -704,6 +704,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -760,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  2 bilder</t>
+          <t>Obs ingår i anmälan a 20538-2025 Rikligt i en radie av ca 50 meter  2 bilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -816,6 +820,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -872,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  3 bilder</t>
+          <t>Obs ingår i anmälan A 20538-2025 Rikligt i en radie av ca 50 meter  3 bilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127720671</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127720568</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127720671</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127720568</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127720671</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127720568</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127720671</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127720568</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127720671</v>
+        <v>127720568</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464559</v>
+        <v>464540</v>
       </c>
       <c r="R2" t="n">
-        <v>6784461</v>
+        <v>6784429</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Obs ingår i anmälan a 20538-2025 Rikligt i en radie av ca 50 meter  2 bilder</t>
+          <t>Obs ingår i anmälan A 20538-2025 Rikligt i en radie av ca 50 meter  3 bilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,14 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127720568</v>
+        <v>127720671</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464540</v>
+        <v>464559</v>
       </c>
       <c r="R3" t="n">
-        <v>6784429</v>
+        <v>6784461</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Obs ingår i anmälan A 20538-2025 Rikligt i en radie av ca 50 meter  3 bilder</t>
+          <t>Obs ingår i anmälan a 20538-2025 Rikligt i en radie av ca 50 meter  2 bilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +904,229 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127720724</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>464597</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6784420</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Obs ingår i anmälan 20538-2025 1 bild med bandad tall, Fiskarheden, i förgrunden.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127720766</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>464581</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6784393</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20538-2025 artfynd.xlsx
+++ b/artfynd/A 20538-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720568</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720671</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720724</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,8 +1147,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>